--- a/INVENTARIOS AUTODECER.xlsx
+++ b/INVENTARIOS AUTODECER.xlsx
@@ -9,7 +9,7 @@
     <sheet name="ARMAS" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="ACCESORIOS" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="COMUNICACIONES" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ORO_093_3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1_ORO_093" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/INVENTARIOS AUTODECER.xlsx
+++ b/INVENTARIOS AUTODECER.xlsx
@@ -2707,10 +2707,8 @@
         </is>
       </c>
       <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="43" t="n">
+        <v>2</v>
       </c>
       <c r="D12" s="146" t="n"/>
       <c r="E12" s="133" t="n"/>
